--- a/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
+++ b/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설치 목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설치 명령어" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네트워크" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증빙 화면" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설치 명령어" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네트워크" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설치 목록'!$A$4:$L$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설치 목록'!$A$4:$O$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +89,12 @@
       <name val="Arial"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -169,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +191,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,6 +226,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -237,7 +251,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -312,6 +326,1236 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>150</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>222</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>258</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>294</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>330</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>366</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>402</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>438</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>474</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>510</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>546</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>582</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>618</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>654</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>690</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>726</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>762</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>798</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>834</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>870</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>906</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>942</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>978</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1014</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1050</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1086</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1194</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1230</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1266</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1302</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1338</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1374</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1410</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1446</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1482</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1518</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1554</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1590</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1626</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1662</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1698</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1734</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="6143625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -603,7 +1847,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -614,10 +1858,13 @@
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,20 +1931,35 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
+          <t>제조사 공식 선언 (원문 그대로)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>선언 페이지</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>증빙 화면 (캡처)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
           <t>OSI 승인 라이선스 페이지</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>증빙 링크 (라이선스 원문)</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>증빙 원문 인용</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>비고 (제공 · 출처의 사실)</t>
         </is>
@@ -744,22 +2006,37 @@
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>[오픈소스 선언] "Windows Subsystem for Linux (WSL) is now Open Source."</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/windows/wsl/opensource</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 4행</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/microsoft/WSL/master/LICENSE</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) Microsoft Corporation."</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -797,2177 +2074,2723 @@
           <t>Docker Subscription Service Agreement</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>[무료 선언] "Docker Desktop is free for: Small businesses (fewer than 250 employees AND less than $10 million in annual revenue) Personal use Education Non-commercial open source projects"</t>
+        </is>
+      </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
           <t>https://docs.docker.com/subscription/desktop-license/</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 40행</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>https://docs.docker.com/subscription/desktop-license/</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>"Docker Desktop is free for: / Small businesses (fewer than 250 employees AND less than $10 million in annual revenue) / Personal use / Education / Non-commercial open source projects"</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>버전 근거: 공식 릴리스 노트 https://docs.docker.com/desktop/release-notes/ 「4.86.0 2026-08-10 … Updates Docker Engine v29.7.2」</t>
         </is>
       </c>
     </row>
     <row r="7" outlineLevel="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ emqx/emqx:5.8</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>MQTT 브로커</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/emqx/emqx</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Apache License 2.0 (기본)</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "EMQX is the world's most scalable open-source [MQTT broker](https://www.emqx.com/en/blog/the-ultimate-guide-to-mqtt-broker-comparison) with a high performance that connects 100M+ IoT devices in 1 cluster, while maintaining 1M message per second throughput and sub-millisecond latency."</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/emqx/emqx/v5.8.6/README.md</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 76행</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/emqx/emqx/v5.8.0/LICENSE</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>"Source code in this repository is variously licensed under below licenses. For Default: Apache License 2.0"</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>지원 종료 2026-02-28: https://www.emqx.com/en/news/a-notice-on-the-emqx-5-8-open-source-version</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ frangoteam/fuxa:latest</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>운전 화면(HMI)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/frangoteam/fuxa</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "The open-source version of FUXA remains fully available and continues to evolve with community contributions."</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/frangoteam/FUXA/master/README.md</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 112행</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/frangoteam/FUXA/master/LICENSE</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2019-2025 frangoteam"</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr"/>
     </row>
     <row r="9" outlineLevel="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ redpandadata/redpanda:v24.2.7</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>이벤트 로그</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>v24.2.7</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/redpandadata/redpanda</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Redpanda Business Source License 1.1</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>[무료 선언 (소스 공개)] "The Community Edition is licensed with the Redpanda Business Source License (BSL). These core features are free and source-available."</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.redpanda.com/current/get-started/licensing/overview/</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 148행</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/redpanda-data/redpanda/dev/licenses/bsl.md</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>"Redpanda Business Source License 1.1" / 공식 문서: "Users cannot provide Redpanda as a commercial streaming or queuing service to others." (https://docs.redpanda.com/streaming/24.2/get-started/licenses/)</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr"/>
     </row>
     <row r="10" outlineLevel="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ redpandadata/console:v2.7.2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>이벤트 로그 관리 화면 (선택 실행)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>v2.7.2</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/redpandadata/console</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Redpanda Business Source License (Community)</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>[무료 선언 (소스 공개)] "Redpanda, Redpanda Console, and Redpanda Connect are available in community and enterprise editions."</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.redpanda.com/current/get-started/licensing/overview/</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 184행</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>https://docs.redpanda.com/24.3/get-started/licensing/overview</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>공식 문서: Community Edition은 Redpanda BSL, 인증 · 역할 기반 권한은 Enterprise 기능</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="O10" s="10" t="inlineStr">
         <is>
           <t>compose.yaml 주석: 선택 프로필(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ timescale/timescaledb:2.17.2-pg16</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>시계열 저장소</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>2.17.2-pg16</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/timescale/timescaledb</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Apache 2.0 + Timescale License(TSL)</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>일부 오픈소스: Apache 2.0 부분은 OSI 승인, Timescale License 부분은 OSI 승인 아님</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
+          <t>[무료 선언] "You can install TimescaleDB Community Edition in your own on-premises or cloud infrastructure and run it for free."</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.tigerdata.com/about/latest/timescaledb-editions/</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 220행</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/timescale/timescaledb/main/LICENSE</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>"Source code in this repository is variously licensed under the Apache License Version 2.0, an Apache compatible license, or the Timescale License."</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="O11" s="10" t="inlineStr">
         <is>
           <t>TSL 안내: https://www.tigerdata.com/legal/licenses</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ grafana/grafana:11.3.0</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>분석 화면</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>11.3.0</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/grafana/grafana</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>GNU AGPL v3</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Grafana open source software enables you to query, visualize, alert on, and explore your metrics, logs, and traces wherever they are stored."</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>https://grafana.com/docs/grafana/latest/introduction/</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 256행</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/agpl-v3</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/grafana/grafana/main/LICENSE</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>"GNU AFFERO GENERAL PUBLIC LICENSE Version 3, 19 November 2007"</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr"/>
     </row>
     <row r="13" outlineLevel="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ prom/prometheus:v2.55.1</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>서비스 감시 (선택 실행)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>v2.55.1</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/prom/prometheus</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Prometheus is 100% open source and community-driven. All components are available under the Apache 2 License on GitHub."</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>https://prometheus.io/</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 292행</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/prometheus/prometheus/main/LICENSE</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="O13" s="10" t="inlineStr">
         <is>
           <t>compose.yaml 주석: 선택 프로필(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="14" outlineLevel="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ neo4j:5.26-community</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>지식 그래프 DB (Neo4j Browser 포함, http://127.0.0.1:7474)</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>5.26-community</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/neo4j</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>GNU GPL v3</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Neo4j Community Edition is an open source product licensed under GPLv3."</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j/neo4j/release/5.26.0/README.asciidoc</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 328행</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/gpl-3-0</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/neo4j/neo4j/release/5.26.0/LICENSE.txt</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>"GNU GENERAL PUBLIC LICENSE Version 3, 29 June 2007"</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
     </row>
     <row r="15" outlineLevel="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ nginx:1.27-alpine</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>포털 웹 화면</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>1.27-alpine</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/nginx</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>BSD 2-Clause</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "NGINX is free and open source software, distributed under the terms of a simplified [2-clause BSD-like license](LICENSE)."</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/nginx/nginx/master/README.md</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 364행</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-2-clause</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>https://nginx.org/LICENSE</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>"Copyright (C) 2002-2021 Igor Sysoev ... Redistribution and use in source and binary forms, with or without modification, are permitted"</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
     </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ python:3.12-slim</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>파이썬 서비스의 바탕 이미지 (2.11의 11개가 이 위에 빌드됨)</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>3.12-slim</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/python</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Python Software Foundation License v2 (이미지 정의는 MIT)</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Python is developed under an OSI-approved open source license, making it freely usable and distributable, even for commercial use."</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>https://www.python.org/about/</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 400행</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
           <t>https://docs.python.org/3/license.html</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>https://docs.python.org/3/license.html</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>"Python software and documentation are licensed under the Python Software Foundation License Version 2." "All Python releases are Open Source"</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
     </row>
     <row r="17" outlineLevel="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ 자체 빌드 서비스 11개 (plant-sim · connect-ingest · cmd-gateway · connect-sink · detector · agent · process · enterprise-sim · effects-mcp · enterprise-mcp · dmn-mcp)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>설비 시뮬레이터 · 수집 · 명령 관문 · 저장 · 감지 · 에이전트 · 프로세스 · 업무 대역 · 도구 서버</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>공개 저장소에 없음: 유엔진이 이미지 파일(tar)로 전달 → docker load, 또는 교육 레포에서 docker compose build (「설치 명령어」 시트 4단계)</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>교육 레포</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/uengine-oss/hyd-iot-edu/claude/hyd-handoff-work-xziutz/compose.yaml</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>유엔진 교육 레포 코드 + 아래 라이브러리</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/uengine-oss/hyd-iot-edu/claude/hyd-handoff-work-xziutz/compose.yaml</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>compose.yaml의 각 서비스 build 정의(Dockerfile: FROM python:3.12-slim, pip install -r requirements.txt)</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="O17" s="10" t="inlineStr">
         <is>
           <t>교육 코드는 유엔진 제공. compose.yaml의 agent-worker(Claude Code 포함)는 수업에서 실행하지 않으므로 목록에서 뺌</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="2">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>2.11.1</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ fastapi</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>0.115.6</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastapi/0.115.6/</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "The MIT License (MIT)"</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/fastapi/fastapi/0.115.6/LICENSE</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 436행</t>
+        </is>
+      </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="M18" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastapi/0.115.6/</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr"/>
+      <c r="O18" s="14" t="inlineStr"/>
     </row>
     <row r="19" outlineLevel="2">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>2.11.2</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ uvicorn</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>0.34.0</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/uvicorn/0.34.0/</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/encode/uvicorn/0.34.0/LICENSE.md</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 472행</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-3-clause</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="M19" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/uvicorn/0.34.0/</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="N19" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr"/>
+      <c r="O19" s="14" t="inlineStr"/>
     </row>
     <row r="20" outlineLevel="2">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>2.11.3</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ pydantic</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>2.10.4</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pydantic/2.10.4/</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "The MIT License (MIT) … Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/pydantic/pydantic/v2.10.4/LICENSE</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 508행</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="M20" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pydantic/2.10.4/</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="L20" s="13" t="inlineStr"/>
+      <c r="O20" s="14" t="inlineStr"/>
     </row>
     <row r="21" outlineLevel="2">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>2.11.4</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ paho-mqtt</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>2.1.0</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/paho-mqtt/2.1.0/</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>EPL-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "This project is dual licensed under the Eclipse Public License 2.0 and the Eclipse Distribution License 1.0"</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/eclipse-paho/paho.mqtt.python/v2.1.0/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 544행</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/epl-2-0</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="M21" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/paho-mqtt/2.1.0/</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="N21" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "EPL-2.0 OR BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr"/>
+      <c r="O21" s="14" t="inlineStr"/>
     </row>
     <row r="22" outlineLevel="2">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>2.11.5</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ aiokafka</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>0.12.0</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/aiokafka/0.12.0/</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Apache Software License</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Apache License"</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aio-libs/aiokafka/v0.12.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 580행</t>
+        </is>
+      </c>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="M22" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/aiokafka/0.12.0/</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache Software License"</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr"/>
+      <c r="O22" s="14" t="inlineStr"/>
     </row>
     <row r="23" outlineLevel="2">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>2.11.6</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ python-snappy</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>0.7.3</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/python-snappy/0.7.3/</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>BSD</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/intake/python-snappy/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 616행</t>
+        </is>
+      </c>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-3-clause</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="M23" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/python-snappy/0.7.3/</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD"</t>
         </is>
       </c>
-      <c r="L23" s="13" t="inlineStr"/>
+      <c r="O23" s="14" t="inlineStr"/>
     </row>
     <row r="24" outlineLevel="2">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>2.11.7</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ lz4</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>4.3.3</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/lz4/4.3.3/</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>BSD License</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/python-lz4/python-lz4/v4.3.3/LICENSE</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 652행</t>
+        </is>
+      </c>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-3-clause</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="M24" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/lz4/4.3.3/</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD License"</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr"/>
+      <c r="O24" s="14" t="inlineStr"/>
     </row>
     <row r="25" outlineLevel="2">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>2.11.8</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ zstandard</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>0.23.0</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/zstandard/0.23.0/</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>BSD</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/indygreg/python-zstandard/0.23.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 688행</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-3-clause</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="M25" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/zstandard/0.23.0/</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="N25" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD"</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr"/>
+      <c r="O25" s="14" t="inlineStr"/>
     </row>
     <row r="26" outlineLevel="2">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>2.11.9</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ psycopg</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>3.2.3</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/psycopg/3.2.3/</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>GNU LGPL v3</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "GNU LESSER GENERAL PUBLIC LICENSE"</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/psycopg/psycopg/3.2.3/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 724행</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/lgpl-3-0</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="M26" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/psycopg/3.2.3/</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="N26" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "GNU LGPL v3"</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr"/>
+      <c r="O26" s="14" t="inlineStr"/>
     </row>
     <row r="27" outlineLevel="2">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>2.11.10</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ neo4j</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>5.27.0</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/neo4j/5.27.0/</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Apache License, Version 2.0</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "distributed under the terms of the Apache License 2.0"</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j/neo4j-python-driver/5.27.0/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 760행</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="M27" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/neo4j/5.27.0/</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache License, Version 2.0"</t>
         </is>
       </c>
-      <c r="L27" s="13" t="inlineStr"/>
+      <c r="O27" s="14" t="inlineStr"/>
     </row>
     <row r="28" outlineLevel="2">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>2.11.11</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ anthropic</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>최신(&gt;=0.40)</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/anthropic/</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/anthropics/anthropic-sdk-python/v1.14.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 796행</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="M28" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/anthropic/</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr"/>
+      <c r="O28" s="14" t="inlineStr"/>
     </row>
     <row r="29" outlineLevel="2">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>2.11.12</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ sqlglot</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>27.24.2</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/sqlglot/27.24.2/</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "MIT License"</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/tobymao/sqlglot/v27.24.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="K29" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 832행</t>
+        </is>
+      </c>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="M29" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/sqlglot/27.24.2/</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="L29" s="13" t="inlineStr"/>
+      <c r="O29" s="14" t="inlineStr"/>
     </row>
     <row r="30" outlineLevel="2">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>2.11.13</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ pypdf</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>5.1.0</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pypdf/5.1.0/</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>BSD License</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/py-pdf/pypdf/5.1.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 868행</t>
+        </is>
+      </c>
+      <c r="L30" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/bsd-3-clause</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="M30" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pypdf/5.1.0/</t>
         </is>
       </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD License"</t>
         </is>
       </c>
-      <c r="L30" s="13" t="inlineStr"/>
+      <c r="O30" s="14" t="inlineStr"/>
     </row>
     <row r="31" outlineLevel="2">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>2.11.14</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ jsonschema</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>4.26.0</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/jsonschema/4.26.0/</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/python-jsonschema/jsonschema/v4.26.0/COPYING</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 904행</t>
+        </is>
+      </c>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="M31" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/jsonschema/4.26.0/</t>
         </is>
       </c>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="N31" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="L31" s="13" t="inlineStr"/>
+      <c r="O31" s="14" t="inlineStr"/>
     </row>
     <row r="32" outlineLevel="2">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>2.11.15</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ cryptography</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>50.0.2</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/cryptography/50.0.2/</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>Apache-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "This software is made available under the terms of *either* of the licenses"</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/pyca/cryptography/50.0.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 940행</t>
+        </is>
+      </c>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="M32" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/cryptography/50.0.2/</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache-2.0 OR BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr"/>
+      <c r="O32" s="14" t="inlineStr"/>
     </row>
     <row r="33" outlineLevel="2">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>2.11.16</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ fastmcp</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>2.13.0.2</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastmcp/2.13.0.2/</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Apache License"</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jlowin/fastmcp/v2.13.0.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 976행</t>
+        </is>
+      </c>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="M33" s="15" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastmcp/2.13.0.2/</t>
         </is>
       </c>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="N33" s="14" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache-2.0"</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr"/>
+      <c r="O33" s="14" t="inlineStr"/>
     </row>
     <row r="34" outlineLevel="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ Supabase 로컬 이미지 (5.1 Supabase CLI가 내려받음)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>업무 데이터베이스</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>자동: supabase start 처음 실행 때 public.ecr.aws/supabase/&lt;이름&gt;으로 내려받음 (미리 받기: 「설치 명령어」 시트 3단계)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>CLI 2.119.0 기준</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/apps/cli-go/pkg/config/templates/Dockerfile</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>아래 각 이미지</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr"/>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
+      <c r="K34" s="10" t="inlineStr"/>
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/apps/cli-go/pkg/config/templates/Dockerfile</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>"FROM supabase/postgres:15.19.0.002 AS pg15" "FROM library/kong:2.8.1 AS kong" "FROM postgrest/postgrest:v16.4 AS postgrest" … (교육 레포 it/supabase/config.toml에서 storage · analytics · pooler는 enabled = false)</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
     </row>
     <row r="35" outlineLevel="2">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>2.12.1</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/postgres:15.19.0.002</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>DB (PostgreSQL 15)</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>15.19.0.002</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/postgres</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>The PostgreSQL License</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "PostgreSQL is released under the PostgreSQL License, a liberal Open Source license, similar to the BSD or MIT licenses."</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
+        <is>
+          <t>https://www.postgresql.org/about/licence/</t>
+        </is>
+      </c>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1012행</t>
+        </is>
+      </c>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/postgresql</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="M35" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/postgres/develop/LICENSE</t>
         </is>
       </c>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>"The PostgreSQL License  Copyright (c) 2020, Supabase"</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr"/>
+      <c r="O35" s="14" t="inlineStr"/>
     </row>
     <row r="36" outlineLevel="2">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>2.12.2</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ kong:2.8.1</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>API 관문</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>2.8.1</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/kong</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "The world’s most adopted open source API gateway"</t>
+        </is>
+      </c>
+      <c r="J36" s="15" t="inlineStr">
+        <is>
+          <t>https://konghq.com/products/kong-gateway</t>
+        </is>
+      </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1048행</t>
+        </is>
+      </c>
+      <c r="L36" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="M36" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/Kong/kong/2.8.1/LICENSE</t>
         </is>
       </c>
-      <c r="K36" s="13" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L36" s="13" t="inlineStr"/>
+      <c r="O36" s="14" t="inlineStr"/>
     </row>
     <row r="37" outlineLevel="2">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>2.12.3</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ postgrest/postgrest:v16.4</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>REST API</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>v16.4</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/postgrest</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "Permission is hereby granted, free of charge, to any person obtaining a copy of this software and associated documentation files (the "Software"), to deal in the Software without restriction, including without limitation the rights to use, copy, modify, merge, publish, distribute, sublicense, and/or sell copies of the Software, and to permit persons to whom the Software is furnished to do so, subject to the following conditions:"</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/PostgREST/postgrest/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1084행</t>
+        </is>
+      </c>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="M37" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/PostgREST/postgrest/main/LICENSE</t>
         </is>
       </c>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="N37" s="14" t="inlineStr">
         <is>
           <t>"Permission is hereby granted, free of charge, to any person"</t>
         </is>
       </c>
-      <c r="L37" s="13" t="inlineStr"/>
+      <c r="O37" s="14" t="inlineStr"/>
     </row>
     <row r="38" outlineLevel="2">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>2.12.4</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/gotrue:v2.197.0</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>v2.197.0</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/gotrue</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Supabase is open source. We choose open source tools which are scalable and make them approachable."</t>
+        </is>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1120행</t>
+        </is>
+      </c>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="M38" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/auth/master/LICENSE</t>
         </is>
       </c>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2021-2025 Supabase"</t>
         </is>
       </c>
-      <c r="L38" s="13" t="inlineStr"/>
+      <c r="O38" s="14" t="inlineStr"/>
     </row>
     <row r="39" outlineLevel="2">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>2.12.5</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/realtime:v2.140.3</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>실시간</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>v2.140.3</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/realtime</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Supabase is open source. We choose open source tools which are scalable and make them approachable."</t>
+        </is>
+      </c>
+      <c r="J39" s="15" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1156행</t>
+        </is>
+      </c>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="M39" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/realtime/main/LICENSE</t>
         </is>
       </c>
-      <c r="K39" s="13" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L39" s="13" t="inlineStr"/>
+      <c r="O39" s="14" t="inlineStr"/>
     </row>
     <row r="40" outlineLevel="2">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>2.12.6</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/studio:2026.09.28-sha-5e59b60</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>DB 관리 화면</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>2026.09.28-sha-5e59b60</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/studio</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "An open source Dashboard for managing your database and services."</t>
+        </is>
+      </c>
+      <c r="J40" s="15" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1192행</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="M40" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/supabase/master/LICENSE</t>
         </is>
       </c>
-      <c r="K40" s="13" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L40" s="13" t="inlineStr"/>
+      <c r="O40" s="14" t="inlineStr"/>
     </row>
     <row r="41" outlineLevel="2">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>2.12.7</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/postgres-meta:v0.99.0</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>관리 화면용 메타 API</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>v0.99.0</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/postgres-meta</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Supabase is open source. We choose open source tools which are scalable and make them approachable."</t>
+        </is>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1228행</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="M41" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/postgres-meta/master/LICENSE</t>
         </is>
       </c>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="N41" s="14" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L41" s="13" t="inlineStr"/>
+      <c r="O41" s="14" t="inlineStr"/>
     </row>
     <row r="42" outlineLevel="2">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>2.12.8</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ axllent/mailpit:v1.31.3</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>메일 시험함</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>v1.31.3</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/mailpit</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Mailpit was developed to provide a performant, modern, open-source utility for testing emails and SMTP delivery."</t>
+        </is>
+      </c>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>https://mailpit.axllent.org/about/</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1264행</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/axllent/mailpit/develop/LICENSE</t>
         </is>
       </c>
-      <c r="K42" s="13" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>"The MIT License (MIT)  Copyright (c) 2022-Now() Ralph Slooten"</t>
         </is>
       </c>
-      <c r="L42" s="13" t="inlineStr"/>
+      <c r="O42" s="14" t="inlineStr"/>
     </row>
     <row r="43" outlineLevel="2">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>2.12.9</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/edge-runtime:v1.77.1</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>함수 실행기 (실행 여부 미확인)</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>v1.77.1</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/edge-runtime</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Today we’re open-sourcing Supabase Edge Runtime for self-hosting Deno Edge Functions."</t>
+        </is>
+      </c>
+      <c r="J43" s="15" t="inlineStr">
+        <is>
+          <t>https://supabase.com/blog/edge-runtime-self-hosted-deno-functions</t>
+        </is>
+      </c>
+      <c r="K43" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1300행</t>
+        </is>
+      </c>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="M43" s="15" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/supabase/edge-runtime/main/LICENSE</t>
         </is>
       </c>
-      <c r="K43" s="13" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2023 Supabase"</t>
         </is>
       </c>
-      <c r="L43" s="13" t="inlineStr"/>
+      <c r="O43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3010,22 +4833,37 @@
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>[오픈소스 선언] "As an open source project, Git for Windows benefits greatly from both the volunteer work of helpful developers and good bug reports made by Git for Windows’ users."</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>https://gitforwindows.org/</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 1336행</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>https://opensource.org/license/gpl-2-0</t>
         </is>
       </c>
-      <c r="J44" s="6" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/git-for-windows/git/v2.56.0.windows.2/COPYING</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>"Note that the only valid version of the GPL as far as this project is concerned is _this_ particular version of the license (ie v2, not v2.2 or v3.x or whatever), unless explicitly otherwise stated."</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>버전 근거: https://gitforwindows.org/latest-version.txt → 2.56.0.2</t>
         </is>
@@ -3072,80 +4910,98 @@
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>[오픈소스 선언] "Python is developed under an OSI-approved open source license, making it freely usable and distributable, even for commercial use."</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.python.org/about/</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 1372행</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>https://docs.python.org/3/license.html</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/python/cpython/v3.14.7/LICENSE</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>v3.14.7 LICENSE: "All Python releases are Open Source (see https://opensource.org for the Open Source Definition)." "PYTHON SOFTWARE FOUNDATION LICENSE VERSION 2"</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>공식 문서 https://docs.python.org/3.14/license.html: "Python software and documentation are licensed under the Python Software Foundation License Version 2."</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="1">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ 추가 라이브러리 없음</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>학생 실습 코드의 import가 표준 라이브러리와 같은 폴더의 파일뿐</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/산출물/실습</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr"/>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
+      <c r="K46" s="10" t="inlineStr"/>
+      <c r="L46" s="10" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr">
         <is>
           <t>https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/산출물/실습</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>실습 코드 폴더</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr"/>
+      <c r="O46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3188,84 +5044,114 @@
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>[오픈소스 선언] "Node.js® is a free, open-source, cross-platform JavaScript runtime environment that lets developers create servers, web apps, command line tools and scripts."</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>https://nodejs.org/en</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 1408행</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/nodejs/node/v24.22.0/LICENSE</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>v24.22.0 LICENSE: "Node.js is licensed for use as follows: … Permission is hereby granted, free of charge, to any person obtaining a copy of this software"</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>버전 근거: https://nodejs.org/dist/index.json (v24.22.0, 2026-10-14, LTS Krypton). 제작자 PC 기록은 주 버전 24</t>
         </is>
       </c>
     </row>
     <row r="48" outlineLevel="1">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ Supabase CLI</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>업무 데이터베이스(로컬 Supabase) 띄우기 → 2.12의 이미지를 내려받음</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>npm i -g supabase</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>2.119.0</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>https://www.npmjs.com/package/supabase/v/2.119.0</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Supabase CLI packages are released under the MIT license."</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/README.md</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 1444행</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr">
         <is>
           <t>https://registry.npmjs.org/supabase/2.119.0</t>
         </is>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>npm 레지스트리 supabase@2.119.0: "license":"MIT"</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr"/>
+      <c r="O48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3303,259 +5189,334 @@
           <t>Microsoft Software License Terms (배포판) · 소스는 MIT</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>[무료 선언] "Yes, VS Code is free for private or commercial use."</t>
+        </is>
+      </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
+          <t>https://code.visualstudio.com/docs/supporting/faq</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 1480행</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
           <t>https://code.visualstudio.com/license</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>"You may use any number of copies of the software to develop and test your applications, including deployment within your internal corporate network." / FAQ https://code.visualstudio.com/docs/supporting/faq: "Is VS Code free? Yes, VS Code is free for private or commercial use."</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>소스 1.142.0 LICENSE.txt: "MIT License  Copyright (c) 2015 - present Microsoft Corporation" (https://raw.githubusercontent.com/microsoft/vscode/1.142.0/LICENSE.txt). 버전 근거: https://update.code.visualstudio.com/api/releases/stable</t>
         </is>
       </c>
     </row>
     <row r="50" outlineLevel="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ GitHub Copilot Chat (VS Code 기본 채팅 기능)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>바이브 코딩 실습(학생의 AI 도구). 모델은 9.1을 연결해 씀</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>따로 설치하지 않음: VS Code의 기본 채팅 에이전트로 지정되어 있음</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>VS Code 1.142.0이 맞는 판을 설정</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/microsoft/vscode/main/product.json</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>MIT (확장 소스) / GitHub License Terms for Extensions (마켓플레이스 배포판)</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>확장 소스는 오픈소스(MIT, OSI 승인) · 마켓플레이스 배포판은 GitHub 이용 조건(무료 설치)</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "Today we reached the first milestone: the GitHub Copilot Chat extension is now open source on GitHub under the MIT license."</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/blogs/2025/06/30/openSourceAIEditorFirstMilestone</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 1516행</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/microsoft/vscode-copilot-chat/main/LICENSE.txt</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>확장 소스 LICENSE.txt: "MIT License  Copyright (c) Microsoft Corporation. All rights reserved." / VS Code product.json: "defaultChatAgent": { "extensionId": "GitHub.copilot", "chatExtensionId": "GitHub.copilot-chat" … } / 배포판 이용 조건(https://github.gallery.vsassets.io/_apis/public/gallery/publisher/GitHub/extension/copilot-chat/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License): "You may install and use any number of copies of Extensions only with GitHub approved software to develop and test your applications."</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="O50" s="10" t="inlineStr">
         <is>
           <t>유료 Copilot 요금제 필요 없음: VS Code 문서 "BYOK models work without signing into a GitHub account and without a Copilot plan." (9.1 링크)</t>
         </is>
       </c>
     </row>
     <row r="51" outlineLevel="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ Python 확장 (ms-python.python)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>5회차 실습 코드 실행(F5)</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.python@2026.10.0 (「설치 명령어」 시트 1단계)</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>2026.10.0 (2026-10-15 최신 안정판)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>https://marketplace.visualstudio.com/items?itemName=ms-python.python</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "MIT License … Permission is hereby granted, free of charge, to any person obtaining a copy of this software"</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/2026.10.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 1552행</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/2026.10.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>"Copyright (c) Microsoft Corporation. All rights reserved. MIT License" / "The Python extension automatically installs other extensions as optional dependencies"</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr"/>
     </row>
     <row r="52" outlineLevel="2">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>6.2.1</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ Pylance (Python 확장이 함께 설치)</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>파이썬 언어 기능</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.vscode-pylance@2026.4.1 (지울 수 있음)</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>2026.4.1</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>https://marketplace.visualstudio.com/items?itemName=ms-python.vscode-pylance</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>Microsoft Software License Terms (Microsoft Pylance Extension for Visual Studio Code)</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>[무료 선언] "The new, free language server offers increased performance and many more features."</t>
+        </is>
+      </c>
+      <c r="J52" s="15" t="inlineStr">
+        <is>
+          <t>https://devblogs.microsoft.com/python/announcing-pylance-fast-feature-rich-language-support-for-python-in-visual-studio-code/</t>
+        </is>
+      </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1588행</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+      <c r="M52" s="15" t="inlineStr">
         <is>
           <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/vscode-pylance/2026.4.1/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="N52" s="14" t="inlineStr">
         <is>
           <t>"You may install and use any number of copies of the software only with Microsoft Visual Studio, Visual Studio for Mac, Visual Studio Code ... to develop and test your applications." / Python 확장 라이선스: "The Pylance extension is only available in binary form and is released under a Microsoft proprietary license"</t>
         </is>
       </c>
-      <c r="L52" s="13" t="inlineStr"/>
+      <c r="O52" s="14" t="inlineStr"/>
     </row>
     <row r="53" outlineLevel="2">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>6.2.2</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ Python Debugger (Python 확장이 함께 설치)</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>디버거</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.debugpy@2026.6.0 (지울 수 있음)</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>2026.6.0</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F53" s="15" t="inlineStr">
         <is>
           <t>https://marketplace.visualstudio.com/items?itemName=ms-python.debugpy</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
+          <t>[오픈소스 (라이선스 원문)] "MIT License … Permission is hereby granted, free of charge, to any person obtaining a copy of this software"</t>
+        </is>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/2026.6.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>보기 → 1624행</t>
+        </is>
+      </c>
+      <c r="L53" s="15" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/mit</t>
         </is>
       </c>
-      <c r="J53" s="14" t="inlineStr">
+      <c r="M53" s="15" t="inlineStr">
         <is>
           <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/2026.6.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="N53" s="14" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) Microsoft Corporation."</t>
         </is>
       </c>
-      <c r="L53" s="13" t="inlineStr"/>
+      <c r="O53" s="14" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3593,23 +5554,38 @@
           <t>Notion 이용 약관 (Free 플랜)</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>[무료 선언] "Free $0 per member / month For individuals to organize personal projects and life."</t>
+        </is>
+      </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
           <t>https://www.notion.com/pricing</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>보기 → 1660행</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.notion.com/pricing</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>Free 플랜: "$0" per member / month — "For individuals to organize personal projects and life."</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>버전 근거: 공식 다운로드 https://www.notion.so/desktop/windows/download 가 Notion Setup 7.38.1.exe로 이어짐</t>
         </is>
@@ -3644,118 +5620,151 @@
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
     </row>
     <row r="56" outlineLevel="1">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ arrows.app</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>1회차 실습: 관계 그리기</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>설치 없음(웹)</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>https://arrows.app/</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>오픈소스 (OSI 승인 라이선스)</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
+          <t>[오픈소스 선언] "In development as an open-source project with core contributors from Neo4j, managed under Neo4j Labs."</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j-labs/arrows.app/main/README.md</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 1696행</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
           <t>https://opensource.org/license/apache-2-0</t>
         </is>
       </c>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="M56" s="11" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/neo4j-labs/arrows.app/main/LICENSE</t>
         </is>
       </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ GitHub 계정 (Copilot Free)</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Copilot 인라인 제안(코드 자동완성)을 쓸 때 로그인. 채팅은 9.1로 계정 없이 됨</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>웹 가입 (무료)</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>https://github.com/</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>GitHub 이용 약관 · Copilot Free 플랜</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="13" t="inlineStr">
         <is>
           <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>[무료 선언] "This plan includes limited access to a selection of Copilot features allowing you to try AI-powered coding assistance at no cost."</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.github.com/en/copilot/get-started/plans</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>보기 → 1732행</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/setup/copilot</t>
         </is>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>"Without a plan, signing in enrolls an eligible account in Copilot Free." "If you don't have a Copilot subscription yet, you'll be signed up for the Copilot Free plan and get a monthly allowance of inline suggestions and AI credits."</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>계정 없이 안 되는 기능 (https://code.visualstudio.com/docs/agent-customization/language-models): "Some features still require a GitHub account: semantic search, inline suggestions (code completions), and features that rely on embeddings."</t>
         </is>
@@ -3777,7 +5786,7 @@
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>유엔진 제공 · 지불</t>
         </is>
@@ -3786,207 +5795,311 @@
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr"/>
       <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ AI 모델 (LiteLLM 중계) — 수업에서 쓰는 모든 AI</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>① Copilot 채팅의 커스텀 모델(6.1에 연결) ② 시스템 에이전트의 요약 · 문서 지식 추출</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>유엔진이 주소 · 키를 알려 줌 (VS Code: 채팅 모델 고르기 → 언어 모델 관리 → Custom Endpoint)</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/agent-customization/language-models</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>유엔진 제공 (학교 설치 · 결제 없음)</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>유엔진 제공 · 지불</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/agent-customization/language-models</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>"Bring Your Own Key (BYOK) lets you connect to any compatible model provider while still using the VS Code chat experience and tools." "BYOK models work without signing into a GitHub account and without a Copilot plan." "The Custom Endpoint provider lets you connect any compatible API endpoint to chat in VS Code." / 과금 (https://code.visualstudio.com/docs/setup/copilot): "If you use a Claude bring-your-own-key (BYOK) configuration, a ChatGPT subscription, or your own model credentials, that provider manages usage and billing instead."</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>이용 비용은 유엔진 지불</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L59"/>
+  <autoFilter ref="A4:O59"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
+    <hyperlink ref="K5" location="'증빙 화면'!A4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId6"/>
+    <hyperlink ref="K6" location="'증빙 화면'!A40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId9"/>
+    <hyperlink ref="K7" location="'증빙 화면'!A76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId13"/>
+    <hyperlink ref="K8" location="'증빙 화면'!A112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId17"/>
+    <hyperlink ref="K9" location="'증빙 화면'!A148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId20"/>
+    <hyperlink ref="K10" location="'증빙 화면'!A184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId23"/>
+    <hyperlink ref="K11" location="'증빙 화면'!A220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId27"/>
+    <hyperlink ref="K12" location="'증빙 화면'!A256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId31"/>
+    <hyperlink ref="K13" location="'증빙 화면'!A292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId35"/>
+    <hyperlink ref="K14" location="'증빙 화면'!A328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId39"/>
+    <hyperlink ref="K15" location="'증빙 화면'!A364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId43"/>
+    <hyperlink ref="K16" location="'증빙 화면'!A400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId49"/>
+    <hyperlink ref="K18" location="'증빙 화면'!A436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
+    <hyperlink ref="K19" location="'증빙 화면'!A472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId57"/>
+    <hyperlink ref="K20" location="'증빙 화면'!A508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId61"/>
+    <hyperlink ref="K21" location="'증빙 화면'!A544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId65"/>
+    <hyperlink ref="K22" location="'증빙 화면'!A580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId69"/>
+    <hyperlink ref="K23" location="'증빙 화면'!A616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId73"/>
+    <hyperlink ref="K24" location="'증빙 화면'!A652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId77"/>
+    <hyperlink ref="K25" location="'증빙 화면'!A688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId81"/>
+    <hyperlink ref="K26" location="'증빙 화면'!A724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId85"/>
+    <hyperlink ref="K27" location="'증빙 화면'!A760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId89"/>
+    <hyperlink ref="K28" location="'증빙 화면'!A796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId93"/>
+    <hyperlink ref="K29" location="'증빙 화면'!A832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId97"/>
+    <hyperlink ref="K30" location="'증빙 화면'!A868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId101"/>
+    <hyperlink ref="K31" location="'증빙 화면'!A904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId105"/>
+    <hyperlink ref="K32" location="'증빙 화면'!A940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId109"/>
+    <hyperlink ref="K33" location="'증빙 화면'!A976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId114"/>
+    <hyperlink ref="K35" location="'증빙 화면'!A1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId117"/>
+    <hyperlink ref="K36" location="'증빙 화면'!A1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId120"/>
+    <hyperlink ref="K37" location="'증빙 화면'!A1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId123"/>
+    <hyperlink ref="K38" location="'증빙 화면'!A1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId126"/>
+    <hyperlink ref="K39" location="'증빙 화면'!A1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId129"/>
+    <hyperlink ref="K40" location="'증빙 화면'!A1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId132"/>
+    <hyperlink ref="K41" location="'증빙 화면'!A1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId135"/>
+    <hyperlink ref="K42" location="'증빙 화면'!A1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId138"/>
+    <hyperlink ref="K43" location="'증빙 화면'!A1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId142"/>
+    <hyperlink ref="K44" location="'증빙 화면'!A1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId146"/>
+    <hyperlink ref="K45" location="'증빙 화면'!A1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId152"/>
+    <hyperlink ref="K47" location="'증빙 화면'!A1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId156"/>
+    <hyperlink ref="K48" location="'증빙 화면'!A1444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId160"/>
+    <hyperlink ref="K49" location="'증빙 화면'!A1480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId163"/>
+    <hyperlink ref="K50" location="'증빙 화면'!A1516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId167"/>
+    <hyperlink ref="K51" location="'증빙 화면'!A1552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId171"/>
+    <hyperlink ref="K52" location="'증빙 화면'!A1588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId174"/>
+    <hyperlink ref="K53" location="'증빙 화면'!A1624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId178"/>
+    <hyperlink ref="K54" location="'증빙 화면'!A1660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId181"/>
+    <hyperlink ref="K56" location="'증빙 화면'!A1696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId185"/>
+    <hyperlink ref="K57" location="'증빙 화면'!A1732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3994,6 +6107,2447 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L1734"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>피지컬 AI 교육과정 — 증빙 화면 (제조사 공식 페이지 캡처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>각 화면은 「설치 목록」의 「선언 페이지」를 브라우저로 열어 찍은 것이다. 노란 칸 · 빨간 테두리가 「제조사 공식 선언」에 옮긴 문장이고, 화면 위 띠에 주소와 캡처 시각을 적었다. 강조와 띠 외에는 페이지를 바꾸지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>WSL2 (Windows Subsystem for Linux) — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="20" t="n"/>
+      <c r="L4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Windows Subsystem for Linux (WSL) is now Open Source."</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/windows/wsl/opensource</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Docker Desktop — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Docker Desktop is free for:"  /  "Education"</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>https://docs.docker.com/subscription/desktop-license/</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>emqx/emqx:5.8 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="20" t="n"/>
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="20" t="n"/>
+      <c r="J76" s="20" t="n"/>
+      <c r="K76" s="20" t="n"/>
+      <c r="L76" s="20" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "EMQX is the world's most scalable open-source"</t>
+        </is>
+      </c>
+      <c r="L77" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/emqx/emqx/v5.8.6/README.md</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>frangoteam/fuxa:latest — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="n"/>
+      <c r="D112" s="20" t="n"/>
+      <c r="E112" s="20" t="n"/>
+      <c r="F112" s="20" t="n"/>
+      <c r="G112" s="20" t="n"/>
+      <c r="H112" s="20" t="n"/>
+      <c r="I112" s="20" t="n"/>
+      <c r="J112" s="20" t="n"/>
+      <c r="K112" s="20" t="n"/>
+      <c r="L112" s="20" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "The open-source version of FUXA remains fully available"</t>
+        </is>
+      </c>
+      <c r="L113" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/frangoteam/FUXA/master/README.md</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>redpandadata/redpanda:v24.2.7 — 무료 선언 (소스 공개)</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="n"/>
+      <c r="D148" s="20" t="n"/>
+      <c r="E148" s="20" t="n"/>
+      <c r="F148" s="20" t="n"/>
+      <c r="G148" s="20" t="n"/>
+      <c r="H148" s="20" t="n"/>
+      <c r="I148" s="20" t="n"/>
+      <c r="J148" s="20" t="n"/>
+      <c r="K148" s="20" t="n"/>
+      <c r="L148" s="20" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "These core features are free and source-available."</t>
+        </is>
+      </c>
+      <c r="L149" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="22" t="inlineStr">
+        <is>
+          <t>https://docs.redpanda.com/current/get-started/licensing/overview/</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="19" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>redpandadata/console:v2.7.2 — 무료 선언 (소스 공개)</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="n"/>
+      <c r="D184" s="20" t="n"/>
+      <c r="E184" s="20" t="n"/>
+      <c r="F184" s="20" t="n"/>
+      <c r="G184" s="20" t="n"/>
+      <c r="H184" s="20" t="n"/>
+      <c r="I184" s="20" t="n"/>
+      <c r="J184" s="20" t="n"/>
+      <c r="K184" s="20" t="n"/>
+      <c r="L184" s="20" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redpanda, Redpanda Console, and Redpanda Connect are available in community and enterprise editions."</t>
+        </is>
+      </c>
+      <c r="L185" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>https://docs.redpanda.com/current/get-started/licensing/overview/</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B220" s="19" t="inlineStr">
+        <is>
+          <t>timescale/timescaledb:2.17.2-pg16 — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C220" s="20" t="n"/>
+      <c r="D220" s="20" t="n"/>
+      <c r="E220" s="20" t="n"/>
+      <c r="F220" s="20" t="n"/>
+      <c r="G220" s="20" t="n"/>
+      <c r="H220" s="20" t="n"/>
+      <c r="I220" s="20" t="n"/>
+      <c r="J220" s="20" t="n"/>
+      <c r="K220" s="20" t="n"/>
+      <c r="L220" s="20" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "run it for free"</t>
+        </is>
+      </c>
+      <c r="L221" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="22" t="inlineStr">
+        <is>
+          <t>https://docs.tigerdata.com/about/latest/timescaledb-editions/</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="19" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B256" s="19" t="inlineStr">
+        <is>
+          <t>grafana/grafana:11.3.0 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C256" s="20" t="n"/>
+      <c r="D256" s="20" t="n"/>
+      <c r="E256" s="20" t="n"/>
+      <c r="F256" s="20" t="n"/>
+      <c r="G256" s="20" t="n"/>
+      <c r="H256" s="20" t="n"/>
+      <c r="I256" s="20" t="n"/>
+      <c r="J256" s="20" t="n"/>
+      <c r="K256" s="20" t="n"/>
+      <c r="L256" s="20" t="n"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Grafana open source software enables you to query, visualize, alert on, and explore your metrics, logs, and traces wherever they are stored."</t>
+        </is>
+      </c>
+      <c r="L257" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="22" t="inlineStr">
+        <is>
+          <t>https://grafana.com/docs/grafana/latest/introduction/</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="19" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B292" s="19" t="inlineStr">
+        <is>
+          <t>prom/prometheus:v2.55.1 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C292" s="20" t="n"/>
+      <c r="D292" s="20" t="n"/>
+      <c r="E292" s="20" t="n"/>
+      <c r="F292" s="20" t="n"/>
+      <c r="G292" s="20" t="n"/>
+      <c r="H292" s="20" t="n"/>
+      <c r="I292" s="20" t="n"/>
+      <c r="J292" s="20" t="n"/>
+      <c r="K292" s="20" t="n"/>
+      <c r="L292" s="20" t="n"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Prometheus is 100% open source and community-driven."</t>
+        </is>
+      </c>
+      <c r="L293" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="22" t="inlineStr">
+        <is>
+          <t>https://prometheus.io/</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="19" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B328" s="19" t="inlineStr">
+        <is>
+          <t>neo4j:5.26-community — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="n"/>
+      <c r="D328" s="20" t="n"/>
+      <c r="E328" s="20" t="n"/>
+      <c r="F328" s="20" t="n"/>
+      <c r="G328" s="20" t="n"/>
+      <c r="H328" s="20" t="n"/>
+      <c r="I328" s="20" t="n"/>
+      <c r="J328" s="20" t="n"/>
+      <c r="K328" s="20" t="n"/>
+      <c r="L328" s="20" t="n"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Neo4j Community Edition is an open source product licensed under GPLv3."</t>
+        </is>
+      </c>
+      <c r="L329" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j/neo4j/release/5.26.0/README.asciidoc</t>
+        </is>
+      </c>
+      <c r="I330" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="19" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B364" s="19" t="inlineStr">
+        <is>
+          <t>nginx:1.27-alpine — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C364" s="20" t="n"/>
+      <c r="D364" s="20" t="n"/>
+      <c r="E364" s="20" t="n"/>
+      <c r="F364" s="20" t="n"/>
+      <c r="G364" s="20" t="n"/>
+      <c r="H364" s="20" t="n"/>
+      <c r="I364" s="20" t="n"/>
+      <c r="J364" s="20" t="n"/>
+      <c r="K364" s="20" t="n"/>
+      <c r="L364" s="20" t="n"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "NGINX is free and open source software"</t>
+        </is>
+      </c>
+      <c r="L365" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/nginx/nginx/master/README.md</t>
+        </is>
+      </c>
+      <c r="I366" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="19" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B400" s="19" t="inlineStr">
+        <is>
+          <t>python:3.12-slim — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C400" s="20" t="n"/>
+      <c r="D400" s="20" t="n"/>
+      <c r="E400" s="20" t="n"/>
+      <c r="F400" s="20" t="n"/>
+      <c r="G400" s="20" t="n"/>
+      <c r="H400" s="20" t="n"/>
+      <c r="I400" s="20" t="n"/>
+      <c r="J400" s="20" t="n"/>
+      <c r="K400" s="20" t="n"/>
+      <c r="L400" s="20" t="n"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Python is developed under an OSI-approved open source license, making it freely usable and distributable, even for commercial use."</t>
+        </is>
+      </c>
+      <c r="L401" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="22" t="inlineStr">
+        <is>
+          <t>https://www.python.org/about/</t>
+        </is>
+      </c>
+      <c r="I402" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="19" t="inlineStr">
+        <is>
+          <t>2.11.1</t>
+        </is>
+      </c>
+      <c r="B436" s="19" t="inlineStr">
+        <is>
+          <t>fastapi — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C436" s="20" t="n"/>
+      <c r="D436" s="20" t="n"/>
+      <c r="E436" s="20" t="n"/>
+      <c r="F436" s="20" t="n"/>
+      <c r="G436" s="20" t="n"/>
+      <c r="H436" s="20" t="n"/>
+      <c r="I436" s="20" t="n"/>
+      <c r="J436" s="20" t="n"/>
+      <c r="K436" s="20" t="n"/>
+      <c r="L436" s="20" t="n"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "The MIT License (MIT)"</t>
+        </is>
+      </c>
+      <c r="L437" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/fastapi/fastapi/0.115.6/LICENSE</t>
+        </is>
+      </c>
+      <c r="I438" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="19" t="inlineStr">
+        <is>
+          <t>2.11.2</t>
+        </is>
+      </c>
+      <c r="B472" s="19" t="inlineStr">
+        <is>
+          <t>uvicorn — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C472" s="20" t="n"/>
+      <c r="D472" s="20" t="n"/>
+      <c r="E472" s="20" t="n"/>
+      <c r="F472" s="20" t="n"/>
+      <c r="G472" s="20" t="n"/>
+      <c r="H472" s="20" t="n"/>
+      <c r="I472" s="20" t="n"/>
+      <c r="J472" s="20" t="n"/>
+      <c r="K472" s="20" t="n"/>
+      <c r="L472" s="20" t="n"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="L473" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/encode/uvicorn/0.34.0/LICENSE.md</t>
+        </is>
+      </c>
+      <c r="I474" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="19" t="inlineStr">
+        <is>
+          <t>2.11.3</t>
+        </is>
+      </c>
+      <c r="B508" s="19" t="inlineStr">
+        <is>
+          <t>pydantic — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C508" s="20" t="n"/>
+      <c r="D508" s="20" t="n"/>
+      <c r="E508" s="20" t="n"/>
+      <c r="F508" s="20" t="n"/>
+      <c r="G508" s="20" t="n"/>
+      <c r="H508" s="20" t="n"/>
+      <c r="I508" s="20" t="n"/>
+      <c r="J508" s="20" t="n"/>
+      <c r="K508" s="20" t="n"/>
+      <c r="L508" s="20" t="n"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "The MIT License (MIT)"  /  "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L509" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/pydantic/pydantic/v2.10.4/LICENSE</t>
+        </is>
+      </c>
+      <c r="I510" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="19" t="inlineStr">
+        <is>
+          <t>2.11.4</t>
+        </is>
+      </c>
+      <c r="B544" s="19" t="inlineStr">
+        <is>
+          <t>paho-mqtt — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C544" s="20" t="n"/>
+      <c r="D544" s="20" t="n"/>
+      <c r="E544" s="20" t="n"/>
+      <c r="F544" s="20" t="n"/>
+      <c r="G544" s="20" t="n"/>
+      <c r="H544" s="20" t="n"/>
+      <c r="I544" s="20" t="n"/>
+      <c r="J544" s="20" t="n"/>
+      <c r="K544" s="20" t="n"/>
+      <c r="L544" s="20" t="n"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "dual licensed under the Eclipse Public License 2.0"</t>
+        </is>
+      </c>
+      <c r="L545" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/eclipse-paho/paho.mqtt.python/v2.1.0/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="I546" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="19" t="inlineStr">
+        <is>
+          <t>2.11.5</t>
+        </is>
+      </c>
+      <c r="B580" s="19" t="inlineStr">
+        <is>
+          <t>aiokafka — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C580" s="20" t="n"/>
+      <c r="D580" s="20" t="n"/>
+      <c r="E580" s="20" t="n"/>
+      <c r="F580" s="20" t="n"/>
+      <c r="G580" s="20" t="n"/>
+      <c r="H580" s="20" t="n"/>
+      <c r="I580" s="20" t="n"/>
+      <c r="J580" s="20" t="n"/>
+      <c r="K580" s="20" t="n"/>
+      <c r="L580" s="20" t="n"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Apache License"</t>
+        </is>
+      </c>
+      <c r="L581" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aio-libs/aiokafka/v0.12.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="I582" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="19" t="inlineStr">
+        <is>
+          <t>2.11.6</t>
+        </is>
+      </c>
+      <c r="B616" s="19" t="inlineStr">
+        <is>
+          <t>python-snappy — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C616" s="20" t="n"/>
+      <c r="D616" s="20" t="n"/>
+      <c r="E616" s="20" t="n"/>
+      <c r="F616" s="20" t="n"/>
+      <c r="G616" s="20" t="n"/>
+      <c r="H616" s="20" t="n"/>
+      <c r="I616" s="20" t="n"/>
+      <c r="J616" s="20" t="n"/>
+      <c r="K616" s="20" t="n"/>
+      <c r="L616" s="20" t="n"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="L617" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/intake/python-snappy/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="I618" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="19" t="inlineStr">
+        <is>
+          <t>2.11.7</t>
+        </is>
+      </c>
+      <c r="B652" s="19" t="inlineStr">
+        <is>
+          <t>lz4 — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C652" s="20" t="n"/>
+      <c r="D652" s="20" t="n"/>
+      <c r="E652" s="20" t="n"/>
+      <c r="F652" s="20" t="n"/>
+      <c r="G652" s="20" t="n"/>
+      <c r="H652" s="20" t="n"/>
+      <c r="I652" s="20" t="n"/>
+      <c r="J652" s="20" t="n"/>
+      <c r="K652" s="20" t="n"/>
+      <c r="L652" s="20" t="n"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="L653" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/python-lz4/python-lz4/v4.3.3/LICENSE</t>
+        </is>
+      </c>
+      <c r="I654" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="19" t="inlineStr">
+        <is>
+          <t>2.11.8</t>
+        </is>
+      </c>
+      <c r="B688" s="19" t="inlineStr">
+        <is>
+          <t>zstandard — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C688" s="20" t="n"/>
+      <c r="D688" s="20" t="n"/>
+      <c r="E688" s="20" t="n"/>
+      <c r="F688" s="20" t="n"/>
+      <c r="G688" s="20" t="n"/>
+      <c r="H688" s="20" t="n"/>
+      <c r="I688" s="20" t="n"/>
+      <c r="J688" s="20" t="n"/>
+      <c r="K688" s="20" t="n"/>
+      <c r="L688" s="20" t="n"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="L689" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="B690" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/indygreg/python-zstandard/0.23.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="I690" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="19" t="inlineStr">
+        <is>
+          <t>2.11.9</t>
+        </is>
+      </c>
+      <c r="B724" s="19" t="inlineStr">
+        <is>
+          <t>psycopg — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C724" s="20" t="n"/>
+      <c r="D724" s="20" t="n"/>
+      <c r="E724" s="20" t="n"/>
+      <c r="F724" s="20" t="n"/>
+      <c r="G724" s="20" t="n"/>
+      <c r="H724" s="20" t="n"/>
+      <c r="I724" s="20" t="n"/>
+      <c r="J724" s="20" t="n"/>
+      <c r="K724" s="20" t="n"/>
+      <c r="L724" s="20" t="n"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "GNU LESSER GENERAL PUBLIC LICENSE"</t>
+        </is>
+      </c>
+      <c r="L725" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="B726" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/psycopg/psycopg/3.2.3/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="I726" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="19" t="inlineStr">
+        <is>
+          <t>2.11.10</t>
+        </is>
+      </c>
+      <c r="B760" s="19" t="inlineStr">
+        <is>
+          <t>neo4j — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C760" s="20" t="n"/>
+      <c r="D760" s="20" t="n"/>
+      <c r="E760" s="20" t="n"/>
+      <c r="F760" s="20" t="n"/>
+      <c r="G760" s="20" t="n"/>
+      <c r="H760" s="20" t="n"/>
+      <c r="I760" s="20" t="n"/>
+      <c r="J760" s="20" t="n"/>
+      <c r="K760" s="20" t="n"/>
+      <c r="L760" s="20" t="n"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "distributed under the terms of the Apache License 2.0"</t>
+        </is>
+      </c>
+      <c r="L761" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="B762" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j/neo4j-python-driver/5.27.0/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="I762" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="19" t="inlineStr">
+        <is>
+          <t>2.11.11</t>
+        </is>
+      </c>
+      <c r="B796" s="19" t="inlineStr">
+        <is>
+          <t>anthropic — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C796" s="20" t="n"/>
+      <c r="D796" s="20" t="n"/>
+      <c r="E796" s="20" t="n"/>
+      <c r="F796" s="20" t="n"/>
+      <c r="G796" s="20" t="n"/>
+      <c r="H796" s="20" t="n"/>
+      <c r="I796" s="20" t="n"/>
+      <c r="J796" s="20" t="n"/>
+      <c r="K796" s="20" t="n"/>
+      <c r="L796" s="20" t="n"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L797" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="B798" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/anthropics/anthropic-sdk-python/v1.14.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="I798" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="19" t="inlineStr">
+        <is>
+          <t>2.11.12</t>
+        </is>
+      </c>
+      <c r="B832" s="19" t="inlineStr">
+        <is>
+          <t>sqlglot — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C832" s="20" t="n"/>
+      <c r="D832" s="20" t="n"/>
+      <c r="E832" s="20" t="n"/>
+      <c r="F832" s="20" t="n"/>
+      <c r="G832" s="20" t="n"/>
+      <c r="H832" s="20" t="n"/>
+      <c r="I832" s="20" t="n"/>
+      <c r="J832" s="20" t="n"/>
+      <c r="K832" s="20" t="n"/>
+      <c r="L832" s="20" t="n"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "MIT License"</t>
+        </is>
+      </c>
+      <c r="L833" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="B834" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/tobymao/sqlglot/v27.24.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="I834" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="19" t="inlineStr">
+        <is>
+          <t>2.11.13</t>
+        </is>
+      </c>
+      <c r="B868" s="19" t="inlineStr">
+        <is>
+          <t>pypdf — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C868" s="20" t="n"/>
+      <c r="D868" s="20" t="n"/>
+      <c r="E868" s="20" t="n"/>
+      <c r="F868" s="20" t="n"/>
+      <c r="G868" s="20" t="n"/>
+      <c r="H868" s="20" t="n"/>
+      <c r="I868" s="20" t="n"/>
+      <c r="J868" s="20" t="n"/>
+      <c r="K868" s="20" t="n"/>
+      <c r="L868" s="20" t="n"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Redistribution and use in source and binary forms"</t>
+        </is>
+      </c>
+      <c r="L869" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="B870" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/py-pdf/pypdf/5.1.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="I870" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:57 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="19" t="inlineStr">
+        <is>
+          <t>2.11.14</t>
+        </is>
+      </c>
+      <c r="B904" s="19" t="inlineStr">
+        <is>
+          <t>jsonschema — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C904" s="20" t="n"/>
+      <c r="D904" s="20" t="n"/>
+      <c r="E904" s="20" t="n"/>
+      <c r="F904" s="20" t="n"/>
+      <c r="G904" s="20" t="n"/>
+      <c r="H904" s="20" t="n"/>
+      <c r="I904" s="20" t="n"/>
+      <c r="J904" s="20" t="n"/>
+      <c r="K904" s="20" t="n"/>
+      <c r="L904" s="20" t="n"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L905" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="B906" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/python-jsonschema/jsonschema/v4.26.0/COPYING</t>
+        </is>
+      </c>
+      <c r="I906" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="19" t="inlineStr">
+        <is>
+          <t>2.11.15</t>
+        </is>
+      </c>
+      <c r="B940" s="19" t="inlineStr">
+        <is>
+          <t>cryptography — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C940" s="20" t="n"/>
+      <c r="D940" s="20" t="n"/>
+      <c r="E940" s="20" t="n"/>
+      <c r="F940" s="20" t="n"/>
+      <c r="G940" s="20" t="n"/>
+      <c r="H940" s="20" t="n"/>
+      <c r="I940" s="20" t="n"/>
+      <c r="J940" s="20" t="n"/>
+      <c r="K940" s="20" t="n"/>
+      <c r="L940" s="20" t="n"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "This software is made available under the terms of *either* of the licenses"</t>
+        </is>
+      </c>
+      <c r="L941" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="B942" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/pyca/cryptography/50.0.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="I942" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="19" t="inlineStr">
+        <is>
+          <t>2.11.16</t>
+        </is>
+      </c>
+      <c r="B976" s="19" t="inlineStr">
+        <is>
+          <t>fastmcp — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C976" s="20" t="n"/>
+      <c r="D976" s="20" t="n"/>
+      <c r="E976" s="20" t="n"/>
+      <c r="F976" s="20" t="n"/>
+      <c r="G976" s="20" t="n"/>
+      <c r="H976" s="20" t="n"/>
+      <c r="I976" s="20" t="n"/>
+      <c r="J976" s="20" t="n"/>
+      <c r="K976" s="20" t="n"/>
+      <c r="L976" s="20" t="n"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Apache License"</t>
+        </is>
+      </c>
+      <c r="L977" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="B978" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jlowin/fastmcp/v2.13.0.2/LICENSE</t>
+        </is>
+      </c>
+      <c r="I978" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:58 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="19" t="inlineStr">
+        <is>
+          <t>2.12.1</t>
+        </is>
+      </c>
+      <c r="B1012" s="19" t="inlineStr">
+        <is>
+          <t>supabase/postgres:15.19.0.002 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1012" s="20" t="n"/>
+      <c r="D1012" s="20" t="n"/>
+      <c r="E1012" s="20" t="n"/>
+      <c r="F1012" s="20" t="n"/>
+      <c r="G1012" s="20" t="n"/>
+      <c r="H1012" s="20" t="n"/>
+      <c r="I1012" s="20" t="n"/>
+      <c r="J1012" s="20" t="n"/>
+      <c r="K1012" s="20" t="n"/>
+      <c r="L1012" s="20" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="B1013" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "a liberal Open Source license"</t>
+        </is>
+      </c>
+      <c r="L1013" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="B1014" s="22" t="inlineStr">
+        <is>
+          <t>https://www.postgresql.org/about/licence/</t>
+        </is>
+      </c>
+      <c r="I1014" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="19" t="inlineStr">
+        <is>
+          <t>2.12.2</t>
+        </is>
+      </c>
+      <c r="B1048" s="19" t="inlineStr">
+        <is>
+          <t>kong:2.8.1 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1048" s="20" t="n"/>
+      <c r="D1048" s="20" t="n"/>
+      <c r="E1048" s="20" t="n"/>
+      <c r="F1048" s="20" t="n"/>
+      <c r="G1048" s="20" t="n"/>
+      <c r="H1048" s="20" t="n"/>
+      <c r="I1048" s="20" t="n"/>
+      <c r="J1048" s="20" t="n"/>
+      <c r="K1048" s="20" t="n"/>
+      <c r="L1048" s="20" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="B1049" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "open source API gateway"</t>
+        </is>
+      </c>
+      <c r="L1049" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="B1050" s="22" t="inlineStr">
+        <is>
+          <t>https://konghq.com/products/kong-gateway</t>
+        </is>
+      </c>
+      <c r="I1050" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="19" t="inlineStr">
+        <is>
+          <t>2.12.3</t>
+        </is>
+      </c>
+      <c r="B1084" s="19" t="inlineStr">
+        <is>
+          <t>postgrest/postgrest:v16.4 — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C1084" s="20" t="n"/>
+      <c r="D1084" s="20" t="n"/>
+      <c r="E1084" s="20" t="n"/>
+      <c r="F1084" s="20" t="n"/>
+      <c r="G1084" s="20" t="n"/>
+      <c r="H1084" s="20" t="n"/>
+      <c r="I1084" s="20" t="n"/>
+      <c r="J1084" s="20" t="n"/>
+      <c r="K1084" s="20" t="n"/>
+      <c r="L1084" s="20" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="B1085" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L1085" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="B1086" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/PostgREST/postgrest/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="I1086" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="19" t="inlineStr">
+        <is>
+          <t>2.12.4</t>
+        </is>
+      </c>
+      <c r="B1120" s="19" t="inlineStr">
+        <is>
+          <t>supabase/gotrue:v2.197.0 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1120" s="20" t="n"/>
+      <c r="D1120" s="20" t="n"/>
+      <c r="E1120" s="20" t="n"/>
+      <c r="F1120" s="20" t="n"/>
+      <c r="G1120" s="20" t="n"/>
+      <c r="H1120" s="20" t="n"/>
+      <c r="I1120" s="20" t="n"/>
+      <c r="J1120" s="20" t="n"/>
+      <c r="K1120" s="20" t="n"/>
+      <c r="L1120" s="20" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="B1121" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Supabase is open source."</t>
+        </is>
+      </c>
+      <c r="L1121" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="B1122" s="22" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="I1122" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="19" t="inlineStr">
+        <is>
+          <t>2.12.5</t>
+        </is>
+      </c>
+      <c r="B1156" s="19" t="inlineStr">
+        <is>
+          <t>supabase/realtime:v2.140.3 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1156" s="20" t="n"/>
+      <c r="D1156" s="20" t="n"/>
+      <c r="E1156" s="20" t="n"/>
+      <c r="F1156" s="20" t="n"/>
+      <c r="G1156" s="20" t="n"/>
+      <c r="H1156" s="20" t="n"/>
+      <c r="I1156" s="20" t="n"/>
+      <c r="J1156" s="20" t="n"/>
+      <c r="K1156" s="20" t="n"/>
+      <c r="L1156" s="20" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="B1157" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Supabase is open source."</t>
+        </is>
+      </c>
+      <c r="L1157" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="B1158" s="22" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="I1158" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:59 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="19" t="inlineStr">
+        <is>
+          <t>2.12.6</t>
+        </is>
+      </c>
+      <c r="B1192" s="19" t="inlineStr">
+        <is>
+          <t>supabase/studio:2026.09.28-sha-5e59b60 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1192" s="20" t="n"/>
+      <c r="D1192" s="20" t="n"/>
+      <c r="E1192" s="20" t="n"/>
+      <c r="F1192" s="20" t="n"/>
+      <c r="G1192" s="20" t="n"/>
+      <c r="H1192" s="20" t="n"/>
+      <c r="I1192" s="20" t="n"/>
+      <c r="J1192" s="20" t="n"/>
+      <c r="K1192" s="20" t="n"/>
+      <c r="L1192" s="20" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="B1193" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "An open source Dashboard for managing your database and services."</t>
+        </is>
+      </c>
+      <c r="L1193" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="B1194" s="22" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="I1194" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 15:00 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="19" t="inlineStr">
+        <is>
+          <t>2.12.7</t>
+        </is>
+      </c>
+      <c r="B1228" s="19" t="inlineStr">
+        <is>
+          <t>supabase/postgres-meta:v0.99.0 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1228" s="20" t="n"/>
+      <c r="D1228" s="20" t="n"/>
+      <c r="E1228" s="20" t="n"/>
+      <c r="F1228" s="20" t="n"/>
+      <c r="G1228" s="20" t="n"/>
+      <c r="H1228" s="20" t="n"/>
+      <c r="I1228" s="20" t="n"/>
+      <c r="J1228" s="20" t="n"/>
+      <c r="K1228" s="20" t="n"/>
+      <c r="L1228" s="20" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="B1229" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Supabase is open source."</t>
+        </is>
+      </c>
+      <c r="L1229" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="B1230" s="22" t="inlineStr">
+        <is>
+          <t>https://supabase.com/docs/guides/getting-started/architecture</t>
+        </is>
+      </c>
+      <c r="I1230" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 15:00 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="19" t="inlineStr">
+        <is>
+          <t>2.12.8</t>
+        </is>
+      </c>
+      <c r="B1264" s="19" t="inlineStr">
+        <is>
+          <t>axllent/mailpit:v1.31.3 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1264" s="20" t="n"/>
+      <c r="D1264" s="20" t="n"/>
+      <c r="E1264" s="20" t="n"/>
+      <c r="F1264" s="20" t="n"/>
+      <c r="G1264" s="20" t="n"/>
+      <c r="H1264" s="20" t="n"/>
+      <c r="I1264" s="20" t="n"/>
+      <c r="J1264" s="20" t="n"/>
+      <c r="K1264" s="20" t="n"/>
+      <c r="L1264" s="20" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="B1265" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "open-source utility for testing emails and SMTP delivery"</t>
+        </is>
+      </c>
+      <c r="L1265" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="B1266" s="22" t="inlineStr">
+        <is>
+          <t>https://mailpit.axllent.org/about/</t>
+        </is>
+      </c>
+      <c r="I1266" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 15:01 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="19" t="inlineStr">
+        <is>
+          <t>2.12.9</t>
+        </is>
+      </c>
+      <c r="B1300" s="19" t="inlineStr">
+        <is>
+          <t>supabase/edge-runtime:v1.77.1 — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1300" s="20" t="n"/>
+      <c r="D1300" s="20" t="n"/>
+      <c r="E1300" s="20" t="n"/>
+      <c r="F1300" s="20" t="n"/>
+      <c r="G1300" s="20" t="n"/>
+      <c r="H1300" s="20" t="n"/>
+      <c r="I1300" s="20" t="n"/>
+      <c r="J1300" s="20" t="n"/>
+      <c r="K1300" s="20" t="n"/>
+      <c r="L1300" s="20" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="B1301" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "open-sourcing Supabase Edge Runtime"</t>
+        </is>
+      </c>
+      <c r="L1301" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="B1302" s="22" t="inlineStr">
+        <is>
+          <t>https://supabase.com/blog/edge-runtime-self-hosted-deno-functions</t>
+        </is>
+      </c>
+      <c r="I1302" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 15:00 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1336" s="19" t="inlineStr">
+        <is>
+          <t>Git for Windows (Git Bash 포함) — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1336" s="20" t="n"/>
+      <c r="D1336" s="20" t="n"/>
+      <c r="E1336" s="20" t="n"/>
+      <c r="F1336" s="20" t="n"/>
+      <c r="G1336" s="20" t="n"/>
+      <c r="H1336" s="20" t="n"/>
+      <c r="I1336" s="20" t="n"/>
+      <c r="J1336" s="20" t="n"/>
+      <c r="K1336" s="20" t="n"/>
+      <c r="L1336" s="20" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="B1337" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "As an open source project, Git for Windows"</t>
+        </is>
+      </c>
+      <c r="L1337" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="B1338" s="22" t="inlineStr">
+        <is>
+          <t>https://gitforwindows.org/</t>
+        </is>
+      </c>
+      <c r="I1338" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1372" s="19" t="inlineStr">
+        <is>
+          <t>Python — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1372" s="20" t="n"/>
+      <c r="D1372" s="20" t="n"/>
+      <c r="E1372" s="20" t="n"/>
+      <c r="F1372" s="20" t="n"/>
+      <c r="G1372" s="20" t="n"/>
+      <c r="H1372" s="20" t="n"/>
+      <c r="I1372" s="20" t="n"/>
+      <c r="J1372" s="20" t="n"/>
+      <c r="K1372" s="20" t="n"/>
+      <c r="L1372" s="20" t="n"/>
+    </row>
+    <row r="1373">
+      <c r="B1373" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Python is developed under an OSI-approved open source license, making it freely usable and distributable, even for commercial use."</t>
+        </is>
+      </c>
+      <c r="L1373" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="B1374" s="22" t="inlineStr">
+        <is>
+          <t>https://www.python.org/about/</t>
+        </is>
+      </c>
+      <c r="I1374" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1408" s="19" t="inlineStr">
+        <is>
+          <t>Node.js — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1408" s="20" t="n"/>
+      <c r="D1408" s="20" t="n"/>
+      <c r="E1408" s="20" t="n"/>
+      <c r="F1408" s="20" t="n"/>
+      <c r="G1408" s="20" t="n"/>
+      <c r="H1408" s="20" t="n"/>
+      <c r="I1408" s="20" t="n"/>
+      <c r="J1408" s="20" t="n"/>
+      <c r="K1408" s="20" t="n"/>
+      <c r="L1408" s="20" t="n"/>
+    </row>
+    <row r="1409">
+      <c r="B1409" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "is a free, open-source, cross-platform JavaScript runtime environment"</t>
+        </is>
+      </c>
+      <c r="L1409" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="B1410" s="22" t="inlineStr">
+        <is>
+          <t>https://nodejs.org/en</t>
+        </is>
+      </c>
+      <c r="I1410" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="19" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B1444" s="19" t="inlineStr">
+        <is>
+          <t>Supabase CLI — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1444" s="20" t="n"/>
+      <c r="D1444" s="20" t="n"/>
+      <c r="E1444" s="20" t="n"/>
+      <c r="F1444" s="20" t="n"/>
+      <c r="G1444" s="20" t="n"/>
+      <c r="H1444" s="20" t="n"/>
+      <c r="I1444" s="20" t="n"/>
+      <c r="J1444" s="20" t="n"/>
+      <c r="K1444" s="20" t="n"/>
+      <c r="L1444" s="20" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="B1445" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Supabase CLI packages are released under the MIT license."</t>
+        </is>
+      </c>
+      <c r="L1445" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="B1446" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/README.md</t>
+        </is>
+      </c>
+      <c r="I1446" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:55 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1480" s="19" t="inlineStr">
+        <is>
+          <t>Visual Studio Code — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C1480" s="20" t="n"/>
+      <c r="D1480" s="20" t="n"/>
+      <c r="E1480" s="20" t="n"/>
+      <c r="F1480" s="20" t="n"/>
+      <c r="G1480" s="20" t="n"/>
+      <c r="H1480" s="20" t="n"/>
+      <c r="I1480" s="20" t="n"/>
+      <c r="J1480" s="20" t="n"/>
+      <c r="K1480" s="20" t="n"/>
+      <c r="L1480" s="20" t="n"/>
+    </row>
+    <row r="1481">
+      <c r="B1481" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "Yes, VS Code is free for private or commercial use."</t>
+        </is>
+      </c>
+      <c r="L1481" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="B1482" s="22" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/docs/supporting/faq</t>
+        </is>
+      </c>
+      <c r="I1482" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="19" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B1516" s="19" t="inlineStr">
+        <is>
+          <t>GitHub Copilot Chat (VS Code 기본 채팅 기능) — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1516" s="20" t="n"/>
+      <c r="D1516" s="20" t="n"/>
+      <c r="E1516" s="20" t="n"/>
+      <c r="F1516" s="20" t="n"/>
+      <c r="G1516" s="20" t="n"/>
+      <c r="H1516" s="20" t="n"/>
+      <c r="I1516" s="20" t="n"/>
+      <c r="J1516" s="20" t="n"/>
+      <c r="K1516" s="20" t="n"/>
+      <c r="L1516" s="20" t="n"/>
+    </row>
+    <row r="1517">
+      <c r="B1517" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "is now open source on GitHub under the MIT license"</t>
+        </is>
+      </c>
+      <c r="L1517" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="B1518" s="22" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/blogs/2025/06/30/openSourceAIEditorFirstMilestone</t>
+        </is>
+      </c>
+      <c r="I1518" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="19" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B1552" s="19" t="inlineStr">
+        <is>
+          <t>Python 확장 (ms-python.python) — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C1552" s="20" t="n"/>
+      <c r="D1552" s="20" t="n"/>
+      <c r="E1552" s="20" t="n"/>
+      <c r="F1552" s="20" t="n"/>
+      <c r="G1552" s="20" t="n"/>
+      <c r="H1552" s="20" t="n"/>
+      <c r="I1552" s="20" t="n"/>
+      <c r="J1552" s="20" t="n"/>
+      <c r="K1552" s="20" t="n"/>
+      <c r="L1552" s="20" t="n"/>
+    </row>
+    <row r="1553">
+      <c r="B1553" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "MIT License"  /  "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L1553" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="B1554" s="22" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/2026.10.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="I1554" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="19" t="inlineStr">
+        <is>
+          <t>6.2.1</t>
+        </is>
+      </c>
+      <c r="B1588" s="19" t="inlineStr">
+        <is>
+          <t>Pylance (Python 확장이 함께 설치) — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C1588" s="20" t="n"/>
+      <c r="D1588" s="20" t="n"/>
+      <c r="E1588" s="20" t="n"/>
+      <c r="F1588" s="20" t="n"/>
+      <c r="G1588" s="20" t="n"/>
+      <c r="H1588" s="20" t="n"/>
+      <c r="I1588" s="20" t="n"/>
+      <c r="J1588" s="20" t="n"/>
+      <c r="K1588" s="20" t="n"/>
+      <c r="L1588" s="20" t="n"/>
+    </row>
+    <row r="1589">
+      <c r="B1589" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "The new, free language server offers increased performance and many more features."</t>
+        </is>
+      </c>
+      <c r="L1589" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="B1590" s="22" t="inlineStr">
+        <is>
+          <t>https://devblogs.microsoft.com/python/announcing-pylance-fast-feature-rich-language-support-for-python-in-visual-studio-code/</t>
+        </is>
+      </c>
+      <c r="I1590" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="19" t="inlineStr">
+        <is>
+          <t>6.2.2</t>
+        </is>
+      </c>
+      <c r="B1624" s="19" t="inlineStr">
+        <is>
+          <t>Python Debugger (Python 확장이 함께 설치) — 오픈소스 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="C1624" s="20" t="n"/>
+      <c r="D1624" s="20" t="n"/>
+      <c r="E1624" s="20" t="n"/>
+      <c r="F1624" s="20" t="n"/>
+      <c r="G1624" s="20" t="n"/>
+      <c r="H1624" s="20" t="n"/>
+      <c r="I1624" s="20" t="n"/>
+      <c r="J1624" s="20" t="n"/>
+      <c r="K1624" s="20" t="n"/>
+      <c r="L1624" s="20" t="n"/>
+    </row>
+    <row r="1625">
+      <c r="B1625" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "MIT License"  /  "Permission is hereby granted, free of charge"</t>
+        </is>
+      </c>
+      <c r="L1625" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="B1626" s="22" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/2026.6.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="I1626" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1660" s="19" t="inlineStr">
+        <is>
+          <t>Notion 데스크톱 앱 — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C1660" s="20" t="n"/>
+      <c r="D1660" s="20" t="n"/>
+      <c r="E1660" s="20" t="n"/>
+      <c r="F1660" s="20" t="n"/>
+      <c r="G1660" s="20" t="n"/>
+      <c r="H1660" s="20" t="n"/>
+      <c r="I1660" s="20" t="n"/>
+      <c r="J1660" s="20" t="n"/>
+      <c r="K1660" s="20" t="n"/>
+      <c r="L1660" s="20" t="n"/>
+    </row>
+    <row r="1661">
+      <c r="B1661" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "For individuals to organize personal projects and life."</t>
+        </is>
+      </c>
+      <c r="L1661" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="B1662" s="22" t="inlineStr">
+        <is>
+          <t>https://www.notion.com/pricing</t>
+        </is>
+      </c>
+      <c r="I1662" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="19" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B1696" s="19" t="inlineStr">
+        <is>
+          <t>arrows.app — 오픈소스 선언</t>
+        </is>
+      </c>
+      <c r="C1696" s="20" t="n"/>
+      <c r="D1696" s="20" t="n"/>
+      <c r="E1696" s="20" t="n"/>
+      <c r="F1696" s="20" t="n"/>
+      <c r="G1696" s="20" t="n"/>
+      <c r="H1696" s="20" t="n"/>
+      <c r="I1696" s="20" t="n"/>
+      <c r="J1696" s="20" t="n"/>
+      <c r="K1696" s="20" t="n"/>
+      <c r="L1696" s="20" t="n"/>
+    </row>
+    <row r="1697">
+      <c r="B1697" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "In development as an open-source project"</t>
+        </is>
+      </c>
+      <c r="L1697" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="B1698" s="22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j-labs/arrows.app/main/README.md</t>
+        </is>
+      </c>
+      <c r="I1698" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="19" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B1732" s="19" t="inlineStr">
+        <is>
+          <t>GitHub 계정 (Copilot Free) — 무료 선언</t>
+        </is>
+      </c>
+      <c r="C1732" s="20" t="n"/>
+      <c r="D1732" s="20" t="n"/>
+      <c r="E1732" s="20" t="n"/>
+      <c r="F1732" s="20" t="n"/>
+      <c r="G1732" s="20" t="n"/>
+      <c r="H1732" s="20" t="n"/>
+      <c r="I1732" s="20" t="n"/>
+      <c r="J1732" s="20" t="n"/>
+      <c r="K1732" s="20" t="n"/>
+      <c r="L1732" s="20" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="B1733" s="21" t="inlineStr">
+        <is>
+          <t>강조한 문장: "at no cost"</t>
+        </is>
+      </c>
+      <c r="L1733" s="22" t="inlineStr">
+        <is>
+          <t>← 설치 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="B1734" s="22" t="inlineStr">
+        <is>
+          <t>https://docs.github.com/en/copilot/get-started/plans</t>
+        </is>
+      </c>
+      <c r="I1734" s="3" t="inlineStr">
+        <is>
+          <t>캡처 2026-10-15 14:56 KST</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L5" location="'설치 목록'!A5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+    <hyperlink ref="L41" location="'설치 목록'!A6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
+    <hyperlink ref="L77" location="'설치 목록'!A7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId3"/>
+    <hyperlink ref="L113" location="'설치 목록'!A8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId4"/>
+    <hyperlink ref="L149" location="'설치 목록'!A9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId5"/>
+    <hyperlink ref="L185" location="'설치 목록'!A10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId6"/>
+    <hyperlink ref="L221" location="'설치 목록'!A11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId7"/>
+    <hyperlink ref="L257" location="'설치 목록'!A12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B258" r:id="rId8"/>
+    <hyperlink ref="L293" location="'설치 목록'!A13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B294" r:id="rId9"/>
+    <hyperlink ref="L329" location="'설치 목록'!A14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B330" r:id="rId10"/>
+    <hyperlink ref="L365" location="'설치 목록'!A15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B366" r:id="rId11"/>
+    <hyperlink ref="L401" location="'설치 목록'!A16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B402" r:id="rId12"/>
+    <hyperlink ref="L437" location="'설치 목록'!A18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B438" r:id="rId13"/>
+    <hyperlink ref="L473" location="'설치 목록'!A19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B474" r:id="rId14"/>
+    <hyperlink ref="L509" location="'설치 목록'!A20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B510" r:id="rId15"/>
+    <hyperlink ref="L545" location="'설치 목록'!A21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B546" r:id="rId16"/>
+    <hyperlink ref="L581" location="'설치 목록'!A22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B582" r:id="rId17"/>
+    <hyperlink ref="L617" location="'설치 목록'!A23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B618" r:id="rId18"/>
+    <hyperlink ref="L653" location="'설치 목록'!A24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B654" r:id="rId19"/>
+    <hyperlink ref="L689" location="'설치 목록'!A25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId20"/>
+    <hyperlink ref="L725" location="'설치 목록'!A26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B726" r:id="rId21"/>
+    <hyperlink ref="L761" location="'설치 목록'!A27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B762" r:id="rId22"/>
+    <hyperlink ref="L797" location="'설치 목록'!A28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B798" r:id="rId23"/>
+    <hyperlink ref="L833" location="'설치 목록'!A29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B834" r:id="rId24"/>
+    <hyperlink ref="L869" location="'설치 목록'!A30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B870" r:id="rId25"/>
+    <hyperlink ref="L905" location="'설치 목록'!A31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B906" r:id="rId26"/>
+    <hyperlink ref="L941" location="'설치 목록'!A32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B942" r:id="rId27"/>
+    <hyperlink ref="L977" location="'설치 목록'!A33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B978" r:id="rId28"/>
+    <hyperlink ref="L1013" location="'설치 목록'!A35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1014" r:id="rId29"/>
+    <hyperlink ref="L1049" location="'설치 목록'!A36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1050" r:id="rId30"/>
+    <hyperlink ref="L1085" location="'설치 목록'!A37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1086" r:id="rId31"/>
+    <hyperlink ref="L1121" location="'설치 목록'!A38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1122" r:id="rId32"/>
+    <hyperlink ref="L1157" location="'설치 목록'!A39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1158" r:id="rId33"/>
+    <hyperlink ref="L1193" location="'설치 목록'!A40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1194" r:id="rId34"/>
+    <hyperlink ref="L1229" location="'설치 목록'!A41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1230" r:id="rId35"/>
+    <hyperlink ref="L1265" location="'설치 목록'!A42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1266" r:id="rId36"/>
+    <hyperlink ref="L1301" location="'설치 목록'!A43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1302" r:id="rId37"/>
+    <hyperlink ref="L1337" location="'설치 목록'!A44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1338" r:id="rId38"/>
+    <hyperlink ref="L1373" location="'설치 목록'!A45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1374" r:id="rId39"/>
+    <hyperlink ref="L1409" location="'설치 목록'!A47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1410" r:id="rId40"/>
+    <hyperlink ref="L1445" location="'설치 목록'!A48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1446" r:id="rId41"/>
+    <hyperlink ref="L1481" location="'설치 목록'!A49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1482" r:id="rId42"/>
+    <hyperlink ref="L1517" location="'설치 목록'!A50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1518" r:id="rId43"/>
+    <hyperlink ref="L1553" location="'설치 목록'!A51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1554" r:id="rId44"/>
+    <hyperlink ref="L1589" location="'설치 목록'!A52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1590" r:id="rId45"/>
+    <hyperlink ref="L1625" location="'설치 목록'!A53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1626" r:id="rId46"/>
+    <hyperlink ref="L1661" location="'설치 목록'!A54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1662" r:id="rId47"/>
+    <hyperlink ref="L1697" location="'설치 목록'!A56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1698" r:id="rId48"/>
+    <hyperlink ref="L1733" location="'설치 목록'!A57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1734" r:id="rId49"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="49" manualBreakCount="49">
+    <brk id="39" min="0" max="16383" man="1"/>
+    <brk id="75" min="0" max="16383" man="1"/>
+    <brk id="111" min="0" max="16383" man="1"/>
+    <brk id="147" min="0" max="16383" man="1"/>
+    <brk id="183" min="0" max="16383" man="1"/>
+    <brk id="219" min="0" max="16383" man="1"/>
+    <brk id="255" min="0" max="16383" man="1"/>
+    <brk id="291" min="0" max="16383" man="1"/>
+    <brk id="327" min="0" max="16383" man="1"/>
+    <brk id="363" min="0" max="16383" man="1"/>
+    <brk id="399" min="0" max="16383" man="1"/>
+    <brk id="435" min="0" max="16383" man="1"/>
+    <brk id="471" min="0" max="16383" man="1"/>
+    <brk id="507" min="0" max="16383" man="1"/>
+    <brk id="543" min="0" max="16383" man="1"/>
+    <brk id="579" min="0" max="16383" man="1"/>
+    <brk id="615" min="0" max="16383" man="1"/>
+    <brk id="651" min="0" max="16383" man="1"/>
+    <brk id="687" min="0" max="16383" man="1"/>
+    <brk id="723" min="0" max="16383" man="1"/>
+    <brk id="759" min="0" max="16383" man="1"/>
+    <brk id="795" min="0" max="16383" man="1"/>
+    <brk id="831" min="0" max="16383" man="1"/>
+    <brk id="867" min="0" max="16383" man="1"/>
+    <brk id="903" min="0" max="16383" man="1"/>
+    <brk id="939" min="0" max="16383" man="1"/>
+    <brk id="975" min="0" max="16383" man="1"/>
+    <brk id="1011" min="0" max="16383" man="1"/>
+    <brk id="1047" min="0" max="16383" man="1"/>
+    <brk id="1083" min="0" max="16383" man="1"/>
+    <brk id="1119" min="0" max="16383" man="1"/>
+    <brk id="1155" min="0" max="16383" man="1"/>
+    <brk id="1191" min="0" max="16383" man="1"/>
+    <brk id="1227" min="0" max="16383" man="1"/>
+    <brk id="1263" min="0" max="16383" man="1"/>
+    <brk id="1299" min="0" max="16383" man="1"/>
+    <brk id="1335" min="0" max="16383" man="1"/>
+    <brk id="1371" min="0" max="16383" man="1"/>
+    <brk id="1407" min="0" max="16383" man="1"/>
+    <brk id="1443" min="0" max="16383" man="1"/>
+    <brk id="1479" min="0" max="16383" man="1"/>
+    <brk id="1515" min="0" max="16383" man="1"/>
+    <brk id="1551" min="0" max="16383" man="1"/>
+    <brk id="1587" min="0" max="16383" man="1"/>
+    <brk id="1623" min="0" max="16383" man="1"/>
+    <brk id="1659" min="0" max="16383" man="1"/>
+    <brk id="1695" min="0" max="16383" man="1"/>
+    <brk id="1731" min="0" max="16383" man="1"/>
+    <brk id="1767" min="0" max="16383" man="1"/>
+  </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4016,134 +8570,134 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>프로그램(WSL 제외)은 「설치 목록」 시트의 「받는 곳」에서 공식 설치 파일로 설치한다. 아래는 명령으로 하는 것만 적었다. 명령은 PowerShell · 명령 프롬프트 · bash 어디서나 같다. 단계마다 마지막 줄은 그 단계의 명령 전체를 한 칸에 모은 것이다(한 번에 복사).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>명령어</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>설치 목록 번호</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>1. PC 준비 (관리자 PowerShell, 끝나면 다시 시작)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr"/>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr"/>
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>wsl --install</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Docker Desktop의 기반</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr"/>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr"/>
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>npm install -g supabase@2.119.0</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Node.js(5) 설치 뒤</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr"/>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr"/>
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.vscode-pylance@2026.4.1</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>6.2.1</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>VS Code(6) 설치 뒤. 버전을 고정하려고 Python 확장보다 먼저 설치</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr"/>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr"/>
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.debugpy@2026.6.0</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>6.2.2</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
+      <c r="D9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr"/>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr"/>
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>code --install-extension ms-python.python@2026.10.0</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Copilot 채팅(6.1)은 VS Code 기본 포함이라 명령 없음</t>
         </is>
       </c>
     </row>
     <row r="11" ht="79" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>wsl --install
 npm install -g supabase@2.119.0
@@ -4154,175 +8708,175 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>2. 도커 이미지 내려받기 — Docker Hub</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr"/>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr"/>
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>docker pull emqx/emqx:5.8</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr"/>
+      <c r="D14" s="25" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr"/>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>docker pull frangoteam/fuxa:latest</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>태그가 latest라 받는 날의 최신판</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr"/>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr"/>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>docker pull redpandadata/redpanda:v24.2.7</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr"/>
+      <c r="D16" s="25" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr"/>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr"/>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>docker pull timescale/timescaledb:2.17.2-pg16</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr"/>
+      <c r="D17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr"/>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr"/>
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>docker pull grafana/grafana:11.3.0</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr"/>
+      <c r="D18" s="25" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr"/>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr"/>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>docker pull neo4j:5.26-community</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr"/>
+      <c r="D19" s="25" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr"/>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr"/>
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>docker pull nginx:1.27-alpine</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr"/>
+      <c r="D20" s="25" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr"/>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr"/>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>docker pull python:3.12-slim</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>2.11을 직접 빌드할 때도 바탕</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr"/>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr"/>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>docker pull redpandadata/console:v2.7.2</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>선택 실행(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr"/>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr"/>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>docker pull prom/prometheus:v2.55.1</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>선택 실행(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="154" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>docker pull emqx/emqx:5.8
 docker pull frangoteam/fuxa:latest
@@ -4338,145 +8892,145 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>3. 도커 이미지 내려받기 — Supabase (supabase start가 찾는 이름 그대로)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr"/>
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>2.12.1</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr"/>
+      <c r="D27" s="25" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr"/>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr"/>
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/kong:2.8.1</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>2.12.2</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr"/>
+      <c r="D28" s="25" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr"/>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr"/>
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/postgrest:v16.4</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>2.12.3</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr"/>
+      <c r="D29" s="25" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr"/>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr"/>
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/gotrue:v2.197.0</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>2.12.4</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr"/>
+      <c r="D30" s="25" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr"/>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr"/>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/realtime:v2.140.3</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>2.12.5</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr"/>
+      <c r="D31" s="25" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr"/>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr"/>
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/studio:2026.09.28-sha-5e59b60</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>2.12.6</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr"/>
+      <c r="D32" s="25" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr"/>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr"/>
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/postgres-meta:v0.99.0</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>2.12.7</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr"/>
+      <c r="D33" s="25" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr"/>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr"/>
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/mailpit:v1.31.3</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>2.12.8</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr"/>
+      <c r="D34" s="25" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr"/>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr"/>
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/edge-runtime:v1.77.1</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>2.12.9</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr"/>
+      <c r="D35" s="25" t="inlineStr"/>
     </row>
     <row r="36" ht="139" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002
 docker pull public.ecr.aws/supabase/kong:2.8.1
@@ -4491,90 +9045,90 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>4. 자체 빌드 이미지 11개 넣기 — 방법 A: 유엔진이 전달한 이미지 파일</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr"/>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr"/>
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>docker load -i hyd-iot-edu-images.tar</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="25" t="inlineStr">
         <is>
           <t>파일은 유엔진이 따로 전달(엑셀에 담을 수 없음)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>4. 자체 빌드 이미지 11개 넣기 — 방법 B: 교육 레포에서 직접 빌드 (pypi.org 접속 필요)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr"/>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr"/>
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr"/>
+      <c r="D42" s="25" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr"/>
-      <c r="B43" s="21" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr"/>
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>cd hyd-iot-edu</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="C43" s="25" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr"/>
+      <c r="D43" s="25" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr"/>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr"/>
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>docker compose --profile ot --profile backbone --profile detect --profile knowledge --profile agent --profile enterprise --profile process --profile cliagents build plant-sim connect-ingest cmd-gateway connect-sink detector agent process enterprise-sim effects-mcp enterprise-mcp dmn-mcp</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>프로필 8개를 모두 켜야 서비스 사이 의존이 풀린다(일부만 켜면 "depends on undefined service" 오류)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="49" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git
 cd hyd-iot-edu
@@ -4583,53 +9137,53 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>5. 확인</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr"/>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr"/>
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>docker images</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>2 · 3단계 19개(선택 2개 포함)와 4단계 hyd-iot-edu-* 11개가 보이면 된다</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>확인한 것</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>2단계 이미지 이름 · 태그: 교육 레포 compose.yaml의 image 값 그대로.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>3단계 이미지 이름: Supabase CLI v2.119.0 소스의 규칙 return registry + '/supabase/' + imageName (apps/cli-go/internal/utils/docker.go, 기본 레지스트리 "public.ecr.aws")과 태그 목록(apps/cli-go/pkg/config/templates/Dockerfile). 레지스트리 조회는 postgres-meta만 응답 200을 확인했고 나머지 8개는 요청 제한(429)으로 확인하지 못했다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>4단계 이미지 이름: compose.yaml의 name: hyd-iot-edu에 따라 hyd-iot-edu-&lt;서비스&gt;로 만들어진다. 방법 B 명령은 docker compose config로 검사했다(프로필 8개: 통과, 일부 프로필: depends on undefined service 오류). 빌드 자체는 이 문서를 만든 환경에서 돌리지 않았다.</t>
         </is>
@@ -4653,7 +9207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4675,177 +9229,177 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>무엇을 받는가</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>관련 번호</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>registry-1.docker.io, auth.docker.io, production.cloudflare.docker.com</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>도커 이미지(Docker Hub)</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>2.1~2.10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>public.ecr.aws</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Supabase 이미지</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>pypi.org, files.pythonhosted.org</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>2.11.x</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>registry.npmjs.org</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Supabase CLI</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>marketplace.visualstudio.com</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>VS Code 확장</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>6.1 · 6.2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>github.com, api.github.com</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>GitHub 로그인 · Copilot 인라인 제안</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>www.notion.so, www.notion.com</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>arrows.app</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>관계 그리기</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>유엔진이 알려 주는 AI 모델 주소 (LiteLLM)</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>AI 모델 (Copilot 채팅 · 시스템 에이전트)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>대표 주소다. 제조사가 공개한 전체 방화벽 목록은 각 제조사 문서를 따른다.</t>
         </is>

--- a/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
+++ b/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실습 스택 정보" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명령으로 설치" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증빙 화면" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,11 +50,6 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,7 +115,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -196,186 +189,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>93</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>123</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="5124450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -676,7 +489,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +561,11 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Docker 공식 문서: "Docker Desktop is free for: … Personal use Education Non-commercial open source projects"
-https://docs.docker.com/subscription/desktop-license/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46.5" customHeight="1">
+          <t>증빙1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="33" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -785,8 +597,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Microsoft 공식 문서: "Windows Subsystem for Linux (WSL) is now Open Source."
-https://learn.microsoft.com/en-us/windows/wsl/opensource</t>
+          <t>증빙2.png</t>
         </is>
       </c>
     </row>
@@ -823,12 +634,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>VS Code 공식 FAQ: "Yes, VS Code is free for private or commercial use."
-https://code.visualstudio.com/docs/supporting/faq</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>증빙3.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="33" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -861,12 +671,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>python.org 공식 소개: "Python is developed under an OSI-approved open source license, making it freely usable and distributable, even for commercial use."
-https://www.python.org/about/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>증빙4.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -899,12 +708,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>nodejs.org 공식 첫 화면: "Node.js® is a free, open-source, cross-platform JavaScript runtime environment that lets developers create servers, web apps, command line tools and scripts."
-https://nodejs.org/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="73.5" customHeight="1">
+          <t>증빙5.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46.5" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -936,12 +744,11 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Git for Windows 공식 사이트: "As an open source project, Git for Windows benefits greatly from both the volunteer work of helpful developers and good bug reports made by Git for Windows’ users."
-https://gitforwindows.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46.5" customHeight="1">
+          <t>증빙6.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -973,8 +780,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Notion 공식 요금 안내: "Free $0 per member / month For individuals to organize personal projects and life."
-https://www.notion.com/pricing</t>
+          <t>증빙7.png</t>
         </is>
       </c>
     </row>
@@ -999,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1129,22 +935,94 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>증빙</t>
+          <t>증빙1.png</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>각 행 「증빙」의 문장은 링크한 제조사 공식 페이지의 원문 그대로다. 페이지 캡처는 「증빙 화면」 시트</t>
+          <t>Docker Desktop for Windows — Docker 공식 문서 https://docs.docker.com/subscription/desktop-license/ 캡처(2026-10-15 14:55 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>증빙2.png</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WSL 2 (Linux용 Windows 하위 시스템) — Microsoft 공식 문서 https://learn.microsoft.com/en-us/windows/wsl/opensource 캡처(2026-10-15 14:55 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>증빙3.png</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Visual Studio Code — VS Code 공식 FAQ https://code.visualstudio.com/docs/supporting/faq 캡처(2026-10-15 14:56 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>증빙4.png</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Python — python.org 공식 소개 https://www.python.org/about/ 캡처(2026-10-15 14:55 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>증빙5.png</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Node.js — nodejs.org 공식 첫 화면 https://nodejs.org/en 캡처(2026-10-15 14:55 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>증빙6.png</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Git — Git for Windows 공식 사이트 https://gitforwindows.org/ 캡처(2026-10-15 14:55 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>증빙7.png</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Notion 데스크톱 앱 — Notion 공식 요금 안내 https://www.notion.com/pricing 캡처(2026-10-15 14:56 KST). 노란 칸이 제조사의 무료 · 오픈소스 선언 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>확인일</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
@@ -1238,88 +1116,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A183"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>증빙 화면 — 제조사 공식 페이지 캡처(노란 칸이 「증빙」 열의 문장, 위 띠는 주소와 캡처 시각)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>1. Docker Desktop for Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>2. WSL 2 (Linux용 Windows 하위 시스템)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>3. Visual Studio Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>4. Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>5. Node.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>6. Git</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>7. Notion 데스크톱 앱</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="7" manualBreakCount="7">
-    <brk id="32" min="0" max="16383" man="1"/>
-    <brk id="62" min="0" max="16383" man="1"/>
-    <brk id="92" min="0" max="16383" man="1"/>
-    <brk id="122" min="0" max="16383" man="1"/>
-    <brk id="152" min="0" max="16383" man="1"/>
-    <brk id="182" min="0" max="16383" man="1"/>
-    <brk id="212" min="0" max="16383" man="1"/>
-  </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
+++ b/산출물/설치/피지컬AI_교육_설치목록_라이선스증빙_유엔진솔루션즈.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>증빙1.png</t>
+          <t>1증빙.png</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>증빙2.png</t>
+          <t>2증빙.png</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>증빙3.png</t>
+          <t>3증빙.png</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>증빙4.png</t>
+          <t>4증빙.png</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>증빙5.png</t>
+          <t>5증빙.png</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>증빙6.png</t>
+          <t>6증빙.png</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>증빙7.png</t>
+          <t>7증빙.png</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>증빙1.png</t>
+          <t>1증빙.png</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>증빙2.png</t>
+          <t>2증빙.png</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>증빙3.png</t>
+          <t>3증빙.png</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>증빙4.png</t>
+          <t>4증빙.png</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>증빙5.png</t>
+          <t>5증빙.png</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>증빙6.png</t>
+          <t>6증빙.png</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>증빙7.png</t>
+          <t>7증빙.png</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
